--- a/Content-Strategy/content-calendar.xlsx
+++ b/Content-Strategy/content-calendar.xlsx
@@ -1,85 +1,197 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11015"/>
   <workbookPr/>
-  <workbookProtection/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C518E26-1924-C848-9E60-CAAF9C79DE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Content Calendar" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Content Calendar" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Content Calendar'!$A$4:$G$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Content Calendar'!$1:$4</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+  <si>
+    <t>TAWAL | Behind the Network — LinkedIn Content Calendar</t>
+  </si>
+  <si>
+    <t>Proposed four-week pilot | November 2026 | Student portfolio plan, not an approved TAWAL schedule.</t>
+  </si>
+  <si>
+    <t>Week</t>
+  </si>
+  <si>
+    <t>Proposed date</t>
+  </si>
+  <si>
+    <t>Content topic</t>
+  </si>
+  <si>
+    <t>Format</t>
+  </si>
+  <si>
+    <t>Platform</t>
+  </si>
+  <si>
+    <t>Objective</t>
+  </si>
+  <si>
+    <t>Example caption idea</t>
+  </si>
+  <si>
+    <t>Week 1</t>
+  </si>
+  <si>
+    <t>What digital infrastructure does</t>
+  </si>
+  <si>
+    <t>Short text + labelled illustration</t>
+  </si>
+  <si>
+    <t>LinkedIn</t>
+  </si>
+  <si>
+    <t>Build basic awareness</t>
+  </si>
+  <si>
+    <t>“Connectivity has a physical side. Here is a simple look at the infrastructure that supports it.”</t>
+  </si>
+  <si>
+    <t>Week 2</t>
+  </si>
+  <si>
+    <t>How colocation works</t>
+  </si>
+  <si>
+    <t>3–4 panel carousel</t>
+  </si>
+  <si>
+    <t>Explain infrastructure sharing</t>
+  </si>
+  <si>
+    <t>“One site can support equipment from more than one customer. What does colocation mean in practice?”</t>
+  </si>
+  <si>
+    <t>Week 3</t>
+  </si>
+  <si>
+    <t>Indoor coverage and IBS</t>
+  </si>
+  <si>
+    <t>Short explainer graphic</t>
+  </si>
+  <si>
+    <t>Educate property and venue stakeholders</t>
+  </si>
+  <si>
+    <t>“Outdoor coverage does not always solve an indoor coverage need. Here is what an in-building solution is designed to address.”</t>
+  </si>
+  <si>
+    <t>Week 4</t>
+  </si>
+  <si>
+    <t>How to start an infrastructure conversation</t>
+  </si>
+  <si>
+    <t>Short checklist post</t>
+  </si>
+  <si>
+    <t>Encourage relevant inquiries</t>
+  </si>
+  <si>
+    <t>“Planning a site or building project? These three details can help start a useful conversation: location, need, and timing.”</t>
+  </si>
+  <si>
+    <t>Publishing note: Draft captions and formats require communications and technical review. Use approved links only; no unverified performance, customer, savings, or sustainability claims.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="d mmm yyyy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="d\ mmm\ yyyy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="16"/>
     </font>
     <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF536575"/>
       <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00536575"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF263746"/>
       <name val="Calibri"/>
-      <color rgb="00263746"/>
-      <sz val="10"/>
     </font>
     <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF536575"/>
       <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00536575"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0016324F"/>
+        <fgColor rgb="FF16324F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F7A8C"/>
+        <fgColor rgb="FF1F7A8C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3F6F8"/>
+        <fgColor rgb="FFF3F6F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -92,113 +204,59 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color rgb="00D7E1E8"/>
+        <color rgb="FFD7E1E8"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -486,230 +544,179 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
-    <tabColor rgb="001F7A8C"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <tabColor rgb="FF1F7A8C"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="64" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="13.046875" customWidth="1"/>
+    <col min="2" max="2" width="16.0078125" customWidth="1"/>
+    <col min="3" max="3" width="32.95703125" customWidth="1"/>
+    <col min="4" max="4" width="25.01953125" customWidth="1"/>
+    <col min="5" max="5" width="13.98828125" customWidth="1"/>
+    <col min="6" max="6" width="29.99609375" customWidth="1"/>
+    <col min="7" max="7" width="64.03125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>TAWAL | Behind the Network — LinkedIn Content Calendar</t>
-        </is>
-      </c>
+    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
     </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Proposed four-week pilot | November 2026 | Student portfolio plan, not an approved TAWAL schedule.</t>
-        </is>
-      </c>
+    <row r="2" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Week</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Proposed date</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Content topic</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Objective</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Example caption idea</t>
-        </is>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Week 1</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
+    <row r="5" spans="1:7" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3">
         <v>46329</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>What digital infrastructure does</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Short text + labelled illustration</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Build basic awareness</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>“Connectivity has a physical side. Here is a simple look at the infrastructure that supports it.”</t>
-        </is>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n">
+    <row r="6" spans="1:7" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="5">
         <v>46336</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>How colocation works</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>3–4 panel carousel</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Explain infrastructure sharing</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>“One site can support equipment from more than one customer. What does colocation mean in practice?”</t>
-        </is>
+      <c r="C6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
+    <row r="7" spans="1:7" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="3">
         <v>46343</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Indoor coverage and IBS</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Short explainer graphic</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Educate property and venue stakeholders</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>“Outdoor coverage does not always solve an indoor coverage need. Here is what an in-building solution is designed to address.”</t>
-        </is>
+      <c r="C7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n">
+    <row r="8" spans="1:7" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="5">
         <v>46350</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>How to start an infrastructure conversation</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Short checklist post</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Encourage relevant inquiries</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>“Planning a site or building project? These three details can help start a useful conversation: location, need, and timing.”</t>
-        </is>
+      <c r="C8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Publishing note: Draft captions and formats require communications and technical review. Use approved links only; no unverified performance, customer, savings, or sustainability claims.</t>
-        </is>
-      </c>
+    <row r="10" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G8"/>
+  <autoFilter ref="A4:G8" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="3">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>